--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -2288,10 +2288,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123565029</v>
+        <v>123563516</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>90966</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,55 +2300,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459994</v>
+        <v>459949</v>
       </c>
       <c r="R15" t="n">
-        <v>7021655</v>
+        <v>7021514</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,7 +2363,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2387,12 +2373,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,10 +2405,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123563516</v>
+        <v>123564909</v>
       </c>
       <c r="B16" t="n">
-        <v>90966</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,41 +2417,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459949</v>
+        <v>459981</v>
       </c>
       <c r="R16" t="n">
-        <v>7021514</v>
+        <v>7021650</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2536,7 +2536,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123564909</v>
+        <v>123565029</v>
       </c>
       <c r="B17" t="n">
         <v>98379</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459981</v>
+        <v>459994</v>
       </c>
       <c r="R17" t="n">
-        <v>7021650</v>
+        <v>7021655</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563701</v>
+        <v>123563516</v>
       </c>
       <c r="B2" t="n">
-        <v>56683</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459967</v>
+        <v>459949</v>
       </c>
       <c r="R2" t="n">
-        <v>7021483</v>
+        <v>7021514</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123561186</v>
+        <v>123564909</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +804,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460044</v>
+        <v>459981</v>
       </c>
       <c r="R3" t="n">
-        <v>7021707</v>
+        <v>7021650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123561110</v>
+        <v>123564758</v>
       </c>
       <c r="B4" t="n">
-        <v>79822</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,41 +935,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460053</v>
+        <v>459953</v>
       </c>
       <c r="R4" t="n">
-        <v>7021689</v>
+        <v>7021620</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1042,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,7 +1057,7 @@
         <v>123564707</v>
       </c>
       <c r="B5" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1170,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123563035</v>
+        <v>123563664</v>
       </c>
       <c r="B6" t="n">
-        <v>74869</v>
+        <v>97350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,41 +1197,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459990</v>
+        <v>459959</v>
       </c>
       <c r="R6" t="n">
-        <v>7021593</v>
+        <v>7021511</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1265,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1275,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,22 +1290,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123562820</v>
+        <v>123565489</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,7 +1337,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1341,13 +1356,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460020</v>
+        <v>460067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021656</v>
+        <v>7021711</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,12 +1401,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123564042</v>
+        <v>123565029</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,7 +1468,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1472,13 +1487,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459963</v>
+        <v>459994</v>
       </c>
       <c r="R8" t="n">
-        <v>7021536</v>
+        <v>7021655</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1517,12 +1532,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123565489</v>
+        <v>123562820</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,7 +1599,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1603,13 +1618,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460067</v>
+        <v>460020</v>
       </c>
       <c r="R9" t="n">
-        <v>7021711</v>
+        <v>7021656</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1638,7 +1653,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1648,12 +1663,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123564542</v>
+        <v>123561179</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>77714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,55 +1707,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459947</v>
+        <v>460052</v>
       </c>
       <c r="R10" t="n">
-        <v>7021620</v>
+        <v>7021702</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1769,7 +1770,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1779,12 +1780,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,22 +1800,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123563664</v>
+        <v>123564042</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,31 +1824,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1856,13 +1866,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459959</v>
+        <v>459963</v>
       </c>
       <c r="R11" t="n">
-        <v>7021511</v>
+        <v>7021536</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1891,7 +1901,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1901,7 +1911,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,22 +1931,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123561155</v>
+        <v>123561156</v>
       </c>
       <c r="B12" t="n">
-        <v>74869</v>
+        <v>57857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,41 +1955,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460051</v>
+        <v>460047</v>
       </c>
       <c r="R12" t="n">
-        <v>7021707</v>
+        <v>7021716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2003,7 +2027,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,12 +2037,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,22 +2057,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123561156</v>
+        <v>123563035</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>74875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2057,47 +2081,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460047</v>
+        <v>459990</v>
       </c>
       <c r="R13" t="n">
-        <v>7021716</v>
+        <v>7021593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2144,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2139,12 +2154,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2171,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123561179</v>
+        <v>123563701</v>
       </c>
       <c r="B14" t="n">
-        <v>77708</v>
+        <v>56689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,37 +2202,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460052</v>
+        <v>459967</v>
       </c>
       <c r="R14" t="n">
-        <v>7021702</v>
+        <v>7021483</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2246,7 +2270,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2256,12 +2280,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,10 +2307,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123563516</v>
+        <v>123564542</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,38 +2319,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459949</v>
+        <v>459947</v>
       </c>
       <c r="R15" t="n">
-        <v>7021514</v>
+        <v>7021620</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2363,7 +2396,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2373,12 +2406,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2405,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123564909</v>
+        <v>123561155</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>74875</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2417,55 +2450,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459981</v>
+        <v>460051</v>
       </c>
       <c r="R16" t="n">
-        <v>7021650</v>
+        <v>7021707</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2513,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,12 +2523,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,22 +2543,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123565029</v>
+        <v>123561186</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,40 +2567,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2590,13 +2604,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459994</v>
+        <v>460044</v>
       </c>
       <c r="R17" t="n">
-        <v>7021655</v>
+        <v>7021707</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2649,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123564758</v>
+        <v>123561110</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>79828</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2679,55 +2693,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459953</v>
+        <v>460053</v>
       </c>
       <c r="R18" t="n">
-        <v>7021620</v>
+        <v>7021689</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,12 +2786,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -1943,10 +1943,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123561156</v>
+        <v>123563701</v>
       </c>
       <c r="B12" t="n">
-        <v>57857</v>
+        <v>56689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,20 +1955,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460047</v>
+        <v>459967</v>
       </c>
       <c r="R12" t="n">
-        <v>7021716</v>
+        <v>7021483</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2037,12 +2037,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I gammal barrblandskog</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2057,12 +2052,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2186,10 +2181,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123563701</v>
+        <v>123564542</v>
       </c>
       <c r="B14" t="n">
-        <v>56689</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2198,35 +2193,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459967</v>
+        <v>459947</v>
       </c>
       <c r="R14" t="n">
-        <v>7021483</v>
+        <v>7021620</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2280,7 +2280,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2295,22 +2300,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123564542</v>
+        <v>123561156</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,55 +2324,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459947</v>
+        <v>460047</v>
       </c>
       <c r="R15" t="n">
-        <v>7021620</v>
+        <v>7021716</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563516</v>
+        <v>123563701</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459949</v>
+        <v>459967</v>
       </c>
       <c r="R2" t="n">
-        <v>7021514</v>
+        <v>7021483</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123564909</v>
+        <v>123564707</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459981</v>
+        <v>459953</v>
       </c>
       <c r="R3" t="n">
-        <v>7021650</v>
+        <v>7021635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123564758</v>
+        <v>123561156</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,55 +939,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459953</v>
+        <v>460047</v>
       </c>
       <c r="R4" t="n">
-        <v>7021620</v>
+        <v>7021716</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1021,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123564707</v>
+        <v>123563516</v>
       </c>
       <c r="B5" t="n">
-        <v>105502</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,55 +1065,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459953</v>
+        <v>459949</v>
       </c>
       <c r="R5" t="n">
-        <v>7021635</v>
+        <v>7021514</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,12 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123563664</v>
+        <v>123561110</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>79833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,42 +1186,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>229748</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459959</v>
+        <v>460053</v>
       </c>
       <c r="R6" t="n">
-        <v>7021511</v>
+        <v>7021689</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1275,7 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123565489</v>
+        <v>123561155</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>74878</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,55 +1299,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460067</v>
+        <v>460051</v>
       </c>
       <c r="R7" t="n">
-        <v>7021711</v>
+        <v>7021707</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,12 +1372,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,22 +1392,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123565029</v>
+        <v>123563035</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>74878</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,55 +1416,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459994</v>
+        <v>459990</v>
       </c>
       <c r="R8" t="n">
-        <v>7021655</v>
+        <v>7021593</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1522,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1532,12 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123562820</v>
+        <v>123564542</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,7 +1556,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1618,13 +1575,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460020</v>
+        <v>459947</v>
       </c>
       <c r="R9" t="n">
-        <v>7021656</v>
+        <v>7021620</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1653,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1663,12 +1620,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123561179</v>
+        <v>123564758</v>
       </c>
       <c r="B10" t="n">
-        <v>77714</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,41 +1664,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460052</v>
+        <v>459953</v>
       </c>
       <c r="R10" t="n">
-        <v>7021702</v>
+        <v>7021620</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1770,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1780,12 +1751,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,12 +1771,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1815,7 +1786,7 @@
         <v>123564042</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1943,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123563701</v>
+        <v>123565489</v>
       </c>
       <c r="B12" t="n">
-        <v>56689</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,35 +1926,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1992,13 +1968,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459967</v>
+        <v>460067</v>
       </c>
       <c r="R12" t="n">
-        <v>7021483</v>
+        <v>7021711</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2027,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2037,7 +2013,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,22 +2033,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123563035</v>
+        <v>123564909</v>
       </c>
       <c r="B13" t="n">
-        <v>74875</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,38 +2057,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459990</v>
+        <v>459981</v>
       </c>
       <c r="R13" t="n">
-        <v>7021593</v>
+        <v>7021650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2149,12 +2144,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2181,10 +2176,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123564542</v>
+        <v>123562820</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,7 +2211,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2235,13 +2230,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459947</v>
+        <v>460020</v>
       </c>
       <c r="R14" t="n">
-        <v>7021620</v>
+        <v>7021656</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,7 +2265,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2280,12 +2275,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2312,10 +2307,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123561156</v>
+        <v>123563664</v>
       </c>
       <c r="B15" t="n">
-        <v>57857</v>
+        <v>97367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2328,46 +2323,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460047</v>
+        <v>459959</v>
       </c>
       <c r="R15" t="n">
-        <v>7021716</v>
+        <v>7021511</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2396,7 +2387,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2406,12 +2397,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I gammal barrblandskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,22 +2412,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123561155</v>
+        <v>123561186</v>
       </c>
       <c r="B16" t="n">
-        <v>74875</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2454,37 +2440,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460051</v>
+        <v>460044</v>
       </c>
       <c r="R16" t="n">
         <v>7021707</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,7 +2508,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2523,12 +2518,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,22 +2538,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123561186</v>
+        <v>123565029</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,35 +2562,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460044</v>
+        <v>459994</v>
       </c>
       <c r="R17" t="n">
-        <v>7021707</v>
+        <v>7021655</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123561110</v>
+        <v>123561179</v>
       </c>
       <c r="B18" t="n">
-        <v>79828</v>
+        <v>77719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2693,25 +2693,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460053</v>
+        <v>460052</v>
       </c>
       <c r="R18" t="n">
-        <v>7021689</v>
+        <v>7021702</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563701</v>
+        <v>123563664</v>
       </c>
       <c r="B2" t="n">
-        <v>56692</v>
+        <v>97369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459967</v>
+        <v>459959</v>
       </c>
       <c r="R2" t="n">
-        <v>7021483</v>
+        <v>7021511</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123564707</v>
+        <v>123564758</v>
       </c>
       <c r="B3" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +804,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,10 +849,10 @@
         <v>459953</v>
       </c>
       <c r="R3" t="n">
-        <v>7021635</v>
+        <v>7021620</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123561156</v>
+        <v>123565489</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,50 +935,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460047</v>
+        <v>460067</v>
       </c>
       <c r="R4" t="n">
-        <v>7021716</v>
+        <v>7021711</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123563516</v>
+        <v>123564707</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>105520</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,41 +1066,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459949</v>
+        <v>459953</v>
       </c>
       <c r="R5" t="n">
-        <v>7021514</v>
+        <v>7021635</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,12 +1153,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,7 +1188,7 @@
         <v>123561110</v>
       </c>
       <c r="B6" t="n">
-        <v>79833</v>
+        <v>79835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1287,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123561155</v>
+        <v>123563701</v>
       </c>
       <c r="B7" t="n">
-        <v>74878</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,37 +1318,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460051</v>
+        <v>459967</v>
       </c>
       <c r="R7" t="n">
-        <v>7021707</v>
+        <v>7021483</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,12 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123563035</v>
+        <v>123563516</v>
       </c>
       <c r="B8" t="n">
-        <v>74878</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,21 +1439,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,13 +1463,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459990</v>
+        <v>459949</v>
       </c>
       <c r="R8" t="n">
-        <v>7021593</v>
+        <v>7021514</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,7 +1498,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,12 +1508,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123564542</v>
+        <v>123562820</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,7 +1575,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1575,13 +1594,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459947</v>
+        <v>460020</v>
       </c>
       <c r="R9" t="n">
-        <v>7021620</v>
+        <v>7021656</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1629,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1639,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123564758</v>
+        <v>123561179</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>77721</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,55 +1683,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459953</v>
+        <v>460052</v>
       </c>
       <c r="R10" t="n">
-        <v>7021620</v>
+        <v>7021702</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,22 +1776,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123564042</v>
+        <v>123561155</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>74879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,55 +1800,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459963</v>
+        <v>460051</v>
       </c>
       <c r="R11" t="n">
-        <v>7021536</v>
+        <v>7021707</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1872,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1882,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,22 +1893,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123565489</v>
+        <v>123564542</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1949,7 +1940,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1968,10 +1959,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460067</v>
+        <v>459947</v>
       </c>
       <c r="R12" t="n">
-        <v>7021711</v>
+        <v>7021620</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -2003,7 +1994,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,12 +2004,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2045,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123564909</v>
+        <v>123563035</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>74879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2057,52 +2048,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459981</v>
+        <v>459990</v>
       </c>
       <c r="R13" t="n">
-        <v>7021650</v>
+        <v>7021593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2134,7 +2111,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,12 +2121,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,10 +2153,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123562820</v>
+        <v>123561156</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>57861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2188,55 +2165,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460020</v>
+        <v>460047</v>
       </c>
       <c r="R14" t="n">
-        <v>7021656</v>
+        <v>7021716</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2265,7 +2237,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2275,12 +2247,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2307,10 +2279,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123563664</v>
+        <v>123564042</v>
       </c>
       <c r="B15" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,31 +2291,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2352,13 +2333,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459959</v>
+        <v>459963</v>
       </c>
       <c r="R15" t="n">
-        <v>7021511</v>
+        <v>7021536</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2387,7 +2368,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2397,7 +2378,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2412,12 +2398,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2427,7 +2413,7 @@
         <v>123561186</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2553,7 +2539,7 @@
         <v>123565029</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2681,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123561179</v>
+        <v>123564909</v>
       </c>
       <c r="B18" t="n">
-        <v>77719</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2693,41 +2679,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460052</v>
+        <v>459981</v>
       </c>
       <c r="R18" t="n">
-        <v>7021702</v>
+        <v>7021650</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,12 +2786,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123565489</v>
+        <v>123564707</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>105520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460067</v>
+        <v>459953</v>
       </c>
       <c r="R4" t="n">
-        <v>7021711</v>
+        <v>7021635</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123564707</v>
+        <v>123565489</v>
       </c>
       <c r="B5" t="n">
-        <v>105520</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,30 +1066,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459953</v>
+        <v>460067</v>
       </c>
       <c r="R5" t="n">
-        <v>7021635</v>
+        <v>7021711</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563664</v>
+        <v>123564758</v>
       </c>
       <c r="B2" t="n">
-        <v>97369</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459959</v>
+        <v>459953</v>
       </c>
       <c r="R2" t="n">
-        <v>7021511</v>
+        <v>7021620</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123564758</v>
+        <v>123563664</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>97369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,40 +818,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459953</v>
+        <v>459959</v>
       </c>
       <c r="R3" t="n">
-        <v>7021620</v>
+        <v>7021511</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,12 +911,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123563035</v>
+        <v>123561156</v>
       </c>
       <c r="B13" t="n">
-        <v>74879</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,38 +2048,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459990</v>
+        <v>460047</v>
       </c>
       <c r="R13" t="n">
-        <v>7021593</v>
+        <v>7021716</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,7 +2120,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2121,12 +2130,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,10 +2162,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123561156</v>
+        <v>123564042</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,50 +2174,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460047</v>
+        <v>459963</v>
       </c>
       <c r="R14" t="n">
-        <v>7021716</v>
+        <v>7021536</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2237,7 +2251,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2247,12 +2261,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123564042</v>
+        <v>123563035</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>74879</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,55 +2305,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459963</v>
+        <v>459990</v>
       </c>
       <c r="R15" t="n">
-        <v>7021536</v>
+        <v>7021593</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,10 +2410,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123561186</v>
+        <v>123565029</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2422,35 +2422,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2459,13 +2464,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460044</v>
+        <v>459994</v>
       </c>
       <c r="R16" t="n">
-        <v>7021707</v>
+        <v>7021655</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2499,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,12 +2509,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2536,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123565029</v>
+        <v>123561186</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,40 +2553,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459994</v>
+        <v>460044</v>
       </c>
       <c r="R17" t="n">
-        <v>7021655</v>
+        <v>7021707</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123564758</v>
+        <v>123563664</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459953</v>
+        <v>459959</v>
       </c>
       <c r="R2" t="n">
-        <v>7021620</v>
+        <v>7021511</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123563664</v>
+        <v>123561155</v>
       </c>
       <c r="B3" t="n">
-        <v>97369</v>
+        <v>74879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459959</v>
+        <v>460051</v>
       </c>
       <c r="R3" t="n">
-        <v>7021511</v>
+        <v>7021707</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123564707</v>
+        <v>123564909</v>
       </c>
       <c r="B4" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +921,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459953</v>
+        <v>459981</v>
       </c>
       <c r="R4" t="n">
-        <v>7021635</v>
+        <v>7021650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123565489</v>
+        <v>123563701</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,40 +1052,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1108,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460067</v>
+        <v>459967</v>
       </c>
       <c r="R5" t="n">
-        <v>7021711</v>
+        <v>7021483</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,12 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,22 +1149,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123561110</v>
+        <v>123565489</v>
       </c>
       <c r="B6" t="n">
-        <v>79835</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,41 +1173,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460053</v>
+        <v>460067</v>
       </c>
       <c r="R6" t="n">
-        <v>7021689</v>
+        <v>7021711</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,12 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,22 +1280,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123563701</v>
+        <v>123561110</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>79835</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,50 +1304,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459967</v>
+        <v>460053</v>
       </c>
       <c r="R7" t="n">
-        <v>7021483</v>
+        <v>7021689</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1377,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123563516</v>
+        <v>123563035</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>74879</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,21 +1425,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1463,13 +1449,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459949</v>
+        <v>459990</v>
       </c>
       <c r="R8" t="n">
-        <v>7021514</v>
+        <v>7021593</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1508,12 +1494,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,7 +1529,7 @@
         <v>123562820</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1671,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123561179</v>
+        <v>123561156</v>
       </c>
       <c r="B10" t="n">
-        <v>77721</v>
+        <v>57861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,41 +1669,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460052</v>
+        <v>460047</v>
       </c>
       <c r="R10" t="n">
-        <v>7021702</v>
+        <v>7021716</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1751,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,22 +1771,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123561155</v>
+        <v>123561179</v>
       </c>
       <c r="B11" t="n">
-        <v>74879</v>
+        <v>77721</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,21 +1799,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,13 +1823,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460051</v>
+        <v>460052</v>
       </c>
       <c r="R11" t="n">
-        <v>7021707</v>
+        <v>7021702</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1905,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123564542</v>
+        <v>123565029</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1959,13 +1954,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459947</v>
+        <v>459994</v>
       </c>
       <c r="R12" t="n">
-        <v>7021620</v>
+        <v>7021655</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1994,7 +1989,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2004,12 +1999,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123561156</v>
+        <v>123564707</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>105095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2052,43 +2047,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460047</v>
+        <v>459953</v>
       </c>
       <c r="R13" t="n">
-        <v>7021716</v>
+        <v>7021635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123564042</v>
+        <v>123564758</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459963</v>
+        <v>459953</v>
       </c>
       <c r="R14" t="n">
-        <v>7021536</v>
+        <v>7021620</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123563035</v>
+        <v>123561186</v>
       </c>
       <c r="B15" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,34 +2309,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459990</v>
+        <v>460044</v>
       </c>
       <c r="R15" t="n">
-        <v>7021593</v>
+        <v>7021707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2368,7 +2377,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2378,12 +2387,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123565029</v>
+        <v>123564542</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,7 +2454,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2464,13 +2473,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459994</v>
+        <v>459947</v>
       </c>
       <c r="R16" t="n">
-        <v>7021655</v>
+        <v>7021620</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2499,7 +2508,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2509,12 +2518,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123561186</v>
+        <v>123563516</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,46 +2566,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460044</v>
+        <v>459949</v>
       </c>
       <c r="R17" t="n">
-        <v>7021707</v>
+        <v>7021514</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123564909</v>
+        <v>123564042</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459981</v>
+        <v>459963</v>
       </c>
       <c r="R18" t="n">
-        <v>7021650</v>
+        <v>7021536</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -2419,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123564542</v>
+        <v>123563516</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,52 +2431,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459947</v>
+        <v>459949</v>
       </c>
       <c r="R16" t="n">
-        <v>7021620</v>
+        <v>7021514</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2508,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2518,12 +2504,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2536,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123563516</v>
+        <v>123564542</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,38 +2548,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459949</v>
+        <v>459947</v>
       </c>
       <c r="R17" t="n">
-        <v>7021514</v>
+        <v>7021620</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563664</v>
+        <v>123563701</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459959</v>
+        <v>459967</v>
       </c>
       <c r="R2" t="n">
-        <v>7021511</v>
+        <v>7021483</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123561155</v>
+        <v>123564542</v>
       </c>
       <c r="B3" t="n">
-        <v>74879</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +808,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460051</v>
+        <v>459947</v>
       </c>
       <c r="R3" t="n">
-        <v>7021707</v>
+        <v>7021620</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123564909</v>
+        <v>123563035</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>74879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,52 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459981</v>
+        <v>459990</v>
       </c>
       <c r="R4" t="n">
-        <v>7021650</v>
+        <v>7021593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123563701</v>
+        <v>123561156</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1056,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1089,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459967</v>
+        <v>460047</v>
       </c>
       <c r="R5" t="n">
-        <v>7021483</v>
+        <v>7021716</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,19 +1158,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123565489</v>
+        <v>123564909</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1196,7 +1205,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1215,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460067</v>
+        <v>459981</v>
       </c>
       <c r="R6" t="n">
-        <v>7021711</v>
+        <v>7021650</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,12 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123561110</v>
+        <v>123565489</v>
       </c>
       <c r="B7" t="n">
-        <v>79835</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,41 +1313,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460053</v>
+        <v>460067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021689</v>
+        <v>7021711</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1390,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,12 +1400,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,22 +1420,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123563035</v>
+        <v>123561186</v>
       </c>
       <c r="B8" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,34 +1448,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459990</v>
+        <v>460044</v>
       </c>
       <c r="R8" t="n">
-        <v>7021593</v>
+        <v>7021707</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,12 +1526,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1558,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123562820</v>
+        <v>123564042</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1561,7 +1593,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1580,13 +1612,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460020</v>
+        <v>459963</v>
       </c>
       <c r="R9" t="n">
-        <v>7021656</v>
+        <v>7021536</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,7 +1647,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1625,12 +1657,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,10 +1689,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123561156</v>
+        <v>123564707</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,43 +1705,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460047</v>
+        <v>459953</v>
       </c>
       <c r="R10" t="n">
-        <v>7021716</v>
+        <v>7021635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,7 +1778,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,12 +1788,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123561179</v>
+        <v>123562820</v>
       </c>
       <c r="B11" t="n">
-        <v>77721</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,38 +1832,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460052</v>
+        <v>460020</v>
       </c>
       <c r="R11" t="n">
-        <v>7021702</v>
+        <v>7021656</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1858,7 +1909,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1919,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,22 +1939,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123565029</v>
+        <v>123561155</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>74879</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,55 +1963,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459994</v>
+        <v>460051</v>
       </c>
       <c r="R12" t="n">
-        <v>7021655</v>
+        <v>7021707</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1989,7 +2026,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +2036,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,22 +2056,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123564707</v>
+        <v>123565029</v>
       </c>
       <c r="B13" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2043,30 +2080,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2085,13 +2122,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459953</v>
+        <v>459994</v>
       </c>
       <c r="R13" t="n">
-        <v>7021635</v>
+        <v>7021655</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2120,7 +2157,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,12 +2167,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123564758</v>
+        <v>123561179</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>77721</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,55 +2211,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459953</v>
+        <v>460052</v>
       </c>
       <c r="R14" t="n">
-        <v>7021620</v>
+        <v>7021702</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2251,7 +2274,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2261,12 +2284,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,22 +2304,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123561186</v>
+        <v>123563516</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,46 +2332,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460044</v>
+        <v>459949</v>
       </c>
       <c r="R15" t="n">
-        <v>7021707</v>
+        <v>7021514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,7 +2391,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2387,12 +2401,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,10 +2433,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123563516</v>
+        <v>123563664</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,41 +2445,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459949</v>
+        <v>459959</v>
       </c>
       <c r="R16" t="n">
-        <v>7021514</v>
+        <v>7021511</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2513,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,12 +2523,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,22 +2538,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123564542</v>
+        <v>123561110</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>79835</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,55 +2562,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459947</v>
+        <v>460053</v>
       </c>
       <c r="R17" t="n">
-        <v>7021620</v>
+        <v>7021689</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,19 +2655,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123564042</v>
+        <v>123564758</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459963</v>
+        <v>459953</v>
       </c>
       <c r="R18" t="n">
-        <v>7021536</v>
+        <v>7021620</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123563701</v>
+        <v>123561186</v>
       </c>
       <c r="B2" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459967</v>
+        <v>460044</v>
       </c>
       <c r="R2" t="n">
-        <v>7021483</v>
+        <v>7021707</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123564542</v>
+        <v>123563516</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,52 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459947</v>
+        <v>459949</v>
       </c>
       <c r="R3" t="n">
-        <v>7021620</v>
+        <v>7021514</v>
       </c>
       <c r="S3" t="n">
         <v>6</v>
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123563035</v>
+        <v>123563701</v>
       </c>
       <c r="B4" t="n">
-        <v>74879</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,37 +934,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459990</v>
+        <v>459967</v>
       </c>
       <c r="R4" t="n">
-        <v>7021593</v>
+        <v>7021483</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,12 +1027,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123564909</v>
+        <v>123561110</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>79835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,52 +1177,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459981</v>
+        <v>460053</v>
       </c>
       <c r="R6" t="n">
-        <v>7021650</v>
+        <v>7021689</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1250,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,22 +1270,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123565489</v>
+        <v>123564707</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,30 +1294,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1355,13 +1336,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460067</v>
+        <v>459953</v>
       </c>
       <c r="R7" t="n">
-        <v>7021711</v>
+        <v>7021635</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1400,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,10 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123561186</v>
+        <v>123562820</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,25 +1425,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1472,7 +1453,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1481,13 +1467,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460044</v>
+        <v>460020</v>
       </c>
       <c r="R8" t="n">
-        <v>7021707</v>
+        <v>7021656</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1516,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,12 +1512,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123564042</v>
+        <v>123561179</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>77721</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,55 +1556,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459963</v>
+        <v>460052</v>
       </c>
       <c r="R9" t="n">
-        <v>7021536</v>
+        <v>7021702</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,12 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,22 +1649,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123564707</v>
+        <v>123563035</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>74879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1701,52 +1673,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459953</v>
+        <v>459990</v>
       </c>
       <c r="R10" t="n">
-        <v>7021635</v>
+        <v>7021593</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1778,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1788,12 +1746,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1778,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123562820</v>
+        <v>123561155</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>74879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1832,55 +1790,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460020</v>
+        <v>460051</v>
       </c>
       <c r="R11" t="n">
-        <v>7021656</v>
+        <v>7021707</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1919,12 +1863,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,22 +1883,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123561155</v>
+        <v>123564909</v>
       </c>
       <c r="B12" t="n">
-        <v>74879</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,41 +1907,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460051</v>
+        <v>459981</v>
       </c>
       <c r="R12" t="n">
-        <v>7021707</v>
+        <v>7021650</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2026,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2036,12 +1994,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,19 +2014,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123565029</v>
+        <v>123564542</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2103,7 +2061,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2122,13 +2080,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459994</v>
+        <v>459947</v>
       </c>
       <c r="R13" t="n">
-        <v>7021655</v>
+        <v>7021620</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2157,7 +2115,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2167,12 +2125,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2199,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123561179</v>
+        <v>123564042</v>
       </c>
       <c r="B14" t="n">
-        <v>77721</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2211,41 +2169,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460052</v>
+        <v>459963</v>
       </c>
       <c r="R14" t="n">
-        <v>7021702</v>
+        <v>7021536</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2274,7 +2246,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2284,12 +2256,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2304,22 +2276,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123563516</v>
+        <v>123565489</v>
       </c>
       <c r="B15" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2328,38 +2300,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459949</v>
+        <v>460067</v>
       </c>
       <c r="R15" t="n">
-        <v>7021514</v>
+        <v>7021711</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2391,7 +2377,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2401,12 +2387,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123563664</v>
+        <v>123564758</v>
       </c>
       <c r="B16" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,31 +2431,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2478,13 +2473,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459959</v>
+        <v>459953</v>
       </c>
       <c r="R16" t="n">
-        <v>7021511</v>
+        <v>7021620</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,7 +2508,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2523,7 +2518,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2538,22 +2538,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123561110</v>
+        <v>123563664</v>
       </c>
       <c r="B17" t="n">
-        <v>79835</v>
+        <v>96957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2566,37 +2566,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229748</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460053</v>
+        <v>459959</v>
       </c>
       <c r="R17" t="n">
-        <v>7021689</v>
+        <v>7021511</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2625,7 +2630,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,12 +2640,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,7 +2667,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123564758</v>
+        <v>123565029</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459953</v>
+        <v>459994</v>
       </c>
       <c r="R18" t="n">
-        <v>7021620</v>
+        <v>7021655</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123561186</v>
+        <v>123564909</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460044</v>
+        <v>459981</v>
       </c>
       <c r="R2" t="n">
-        <v>7021707</v>
+        <v>7021650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123563516</v>
+        <v>123563664</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +818,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459949</v>
+        <v>459959</v>
       </c>
       <c r="R3" t="n">
-        <v>7021514</v>
+        <v>7021511</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123563701</v>
+        <v>123565029</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,35 +935,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -967,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459967</v>
+        <v>459994</v>
       </c>
       <c r="R4" t="n">
-        <v>7021483</v>
+        <v>7021655</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,22 +1042,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123561156</v>
+        <v>123565489</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,50 +1066,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460047</v>
+        <v>460067</v>
       </c>
       <c r="R5" t="n">
-        <v>7021716</v>
+        <v>7021711</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,12 +1153,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123561110</v>
+        <v>123561179</v>
       </c>
       <c r="B6" t="n">
-        <v>79835</v>
+        <v>77721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1197,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,13 +1225,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460053</v>
+        <v>460052</v>
       </c>
       <c r="R6" t="n">
-        <v>7021689</v>
+        <v>7021702</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,7 +1260,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,12 +1270,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123564707</v>
+        <v>123564542</v>
       </c>
       <c r="B7" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,30 +1314,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1336,13 +1356,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459953</v>
+        <v>459947</v>
       </c>
       <c r="R7" t="n">
-        <v>7021635</v>
+        <v>7021620</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1371,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1401,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1433,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123562820</v>
+        <v>123564042</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1448,7 +1468,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1467,13 +1487,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460020</v>
+        <v>459963</v>
       </c>
       <c r="R8" t="n">
-        <v>7021656</v>
+        <v>7021536</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,12 +1532,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123561179</v>
+        <v>123564758</v>
       </c>
       <c r="B9" t="n">
-        <v>77721</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,41 +1576,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460052</v>
+        <v>459953</v>
       </c>
       <c r="R9" t="n">
-        <v>7021702</v>
+        <v>7021620</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1653,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,12 +1663,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,22 +1683,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123563035</v>
+        <v>123564707</v>
       </c>
       <c r="B10" t="n">
-        <v>74879</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,38 +1707,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459990</v>
+        <v>459953</v>
       </c>
       <c r="R10" t="n">
-        <v>7021593</v>
+        <v>7021635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1784,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,12 +1794,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1895,10 +1943,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123564909</v>
+        <v>123563516</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,55 +1955,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459981</v>
+        <v>459949</v>
       </c>
       <c r="R12" t="n">
-        <v>7021650</v>
+        <v>7021514</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1984,7 +2018,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1994,12 +2028,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +2060,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123564542</v>
+        <v>123563035</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>74879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,55 +2072,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459947</v>
+        <v>459990</v>
       </c>
       <c r="R13" t="n">
-        <v>7021620</v>
+        <v>7021593</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2115,7 +2135,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2125,12 +2145,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,10 +2177,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123564042</v>
+        <v>123561156</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,55 +2189,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459963</v>
+        <v>460047</v>
       </c>
       <c r="R14" t="n">
-        <v>7021536</v>
+        <v>7021716</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2246,7 +2261,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2256,12 +2271,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,7 +2303,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123565489</v>
+        <v>123562820</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2323,7 +2338,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2342,13 +2357,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460067</v>
+        <v>460020</v>
       </c>
       <c r="R15" t="n">
-        <v>7021711</v>
+        <v>7021656</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2387,12 +2402,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,10 +2434,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123564758</v>
+        <v>123561186</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,40 +2446,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2473,13 +2483,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459953</v>
+        <v>460044</v>
       </c>
       <c r="R16" t="n">
-        <v>7021620</v>
+        <v>7021707</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2508,7 +2518,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2518,12 +2528,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2560,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123563664</v>
+        <v>123563701</v>
       </c>
       <c r="B17" t="n">
-        <v>96957</v>
+        <v>56692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,31 +2572,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2595,13 +2609,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459959</v>
+        <v>459967</v>
       </c>
       <c r="R17" t="n">
-        <v>7021511</v>
+        <v>7021483</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2630,7 +2644,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2640,7 +2654,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123565029</v>
+        <v>123561110</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>79835</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2679,55 +2693,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459994</v>
+        <v>460053</v>
       </c>
       <c r="R18" t="n">
-        <v>7021655</v>
+        <v>7021689</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,12 +2786,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123564909</v>
+        <v>123563035</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>74879</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459981</v>
+        <v>459990</v>
       </c>
       <c r="R2" t="n">
-        <v>7021650</v>
+        <v>7021593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123563664</v>
+        <v>123564909</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,31 +804,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459959</v>
+        <v>459981</v>
       </c>
       <c r="R3" t="n">
-        <v>7021511</v>
+        <v>7021650</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123565029</v>
+        <v>123563701</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,40 +935,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459994</v>
+        <v>459967</v>
       </c>
       <c r="R4" t="n">
-        <v>7021655</v>
+        <v>7021483</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,22 +1032,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123565489</v>
+        <v>123563664</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,40 +1056,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1108,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460067</v>
+        <v>459959</v>
       </c>
       <c r="R5" t="n">
-        <v>7021711</v>
+        <v>7021511</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,12 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,22 +1149,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123561179</v>
+        <v>123565029</v>
       </c>
       <c r="B6" t="n">
-        <v>77721</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,38 +1173,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460052</v>
+        <v>459994</v>
       </c>
       <c r="R6" t="n">
-        <v>7021702</v>
+        <v>7021655</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1260,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,12 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,12 +1280,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1564,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123564758</v>
+        <v>123561156</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,55 +1566,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459953</v>
+        <v>460047</v>
       </c>
       <c r="R9" t="n">
-        <v>7021620</v>
+        <v>7021716</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1653,7 +1638,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1663,12 +1648,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123564707</v>
+        <v>123561155</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>74879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,55 +1692,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459953</v>
+        <v>460051</v>
       </c>
       <c r="R10" t="n">
-        <v>7021635</v>
+        <v>7021707</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1784,7 +1755,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1794,12 +1765,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,22 +1785,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123561155</v>
+        <v>123565489</v>
       </c>
       <c r="B11" t="n">
-        <v>74879</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1838,41 +1809,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460051</v>
+        <v>460067</v>
       </c>
       <c r="R11" t="n">
-        <v>7021707</v>
+        <v>7021711</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1901,7 +1886,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1911,12 +1896,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,22 +1916,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123563516</v>
+        <v>123561186</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1959,37 +1944,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459949</v>
+        <v>460044</v>
       </c>
       <c r="R12" t="n">
-        <v>7021514</v>
+        <v>7021707</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2018,7 +2012,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2028,12 +2022,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,10 +2054,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123563035</v>
+        <v>123561179</v>
       </c>
       <c r="B13" t="n">
-        <v>74879</v>
+        <v>77721</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,21 +2070,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2100,13 +2094,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459990</v>
+        <v>460052</v>
       </c>
       <c r="R13" t="n">
-        <v>7021593</v>
+        <v>7021702</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,7 +2129,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2145,12 +2139,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2165,22 +2159,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123561156</v>
+        <v>123564758</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2189,50 +2183,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460047</v>
+        <v>459953</v>
       </c>
       <c r="R14" t="n">
-        <v>7021716</v>
+        <v>7021620</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2271,12 +2270,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2434,10 +2433,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123561186</v>
+        <v>123561110</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>79835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2446,47 +2445,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460044</v>
+        <v>460053</v>
       </c>
       <c r="R16" t="n">
-        <v>7021707</v>
+        <v>7021689</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,7 +2508,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2528,12 +2518,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2548,22 +2538,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123563701</v>
+        <v>123563516</v>
       </c>
       <c r="B17" t="n">
-        <v>56692</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2576,46 +2566,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459967</v>
+        <v>459949</v>
       </c>
       <c r="R17" t="n">
-        <v>7021483</v>
+        <v>7021514</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2644,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2654,7 +2635,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,22 +2655,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123561110</v>
+        <v>123564707</v>
       </c>
       <c r="B18" t="n">
-        <v>79835</v>
+        <v>105095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2697,34 +2683,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229748</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460053</v>
+        <v>459953</v>
       </c>
       <c r="R18" t="n">
-        <v>7021689</v>
+        <v>7021635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,12 +2786,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123561179</v>
+        <v>123563516</v>
       </c>
       <c r="B2" t="n">
-        <v>77743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460052</v>
+        <v>459949</v>
       </c>
       <c r="R2" t="n">
-        <v>7021702</v>
+        <v>7021514</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,65 +775,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123561155</v>
+        <v>123561186</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460051</v>
+        <v>460044</v>
       </c>
       <c r="R3" t="n">
         <v>7021707</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,79 +896,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123565029</v>
+        <v>123561155</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459994</v>
+        <v>460051</v>
       </c>
       <c r="R4" t="n">
-        <v>7021655</v>
+        <v>7021707</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,79 +1008,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123565489</v>
+        <v>123563035</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460067</v>
+        <v>459990</v>
       </c>
       <c r="R5" t="n">
-        <v>7021711</v>
+        <v>7021593</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,53 +1132,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123563516</v>
+        <v>123563701</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459949</v>
+        <v>459967</v>
       </c>
       <c r="R6" t="n">
-        <v>7021514</v>
+        <v>7021483</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,44 +1236,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123563701</v>
+        <v>123561156</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1333,17 +1288,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sota, Sota, Jmt</t>
+          <t>Sota, Ytterån, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459967</v>
+        <v>460047</v>
       </c>
       <c r="R7" t="n">
-        <v>7021483</v>
+        <v>7021716</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1337,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,59 +1357,59 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123561186</v>
+        <v>123561820</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1458,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460044</v>
+        <v>459984</v>
       </c>
       <c r="R8" t="n">
-        <v>7021707</v>
+        <v>7021738</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,12 +1463,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 16 plantor inom 2x0,3 m</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,53 +1495,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123561110</v>
+        <v>123562820</v>
       </c>
       <c r="B9" t="n">
-        <v>79857</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460053</v>
+        <v>460020</v>
       </c>
       <c r="R9" t="n">
-        <v>7021689</v>
+        <v>7021656</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,65 +1609,74 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123563035</v>
+        <v>123564042</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459990</v>
+        <v>459963</v>
       </c>
       <c r="R10" t="n">
-        <v>7021593</v>
+        <v>7021536</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,12 +1715,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh) i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,15 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123564909</v>
+        <v>123564542</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1777,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1823,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459981</v>
+        <v>459947</v>
       </c>
       <c r="R11" t="n">
-        <v>7021650</v>
+        <v>7021620</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1841,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
+          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,42 +1873,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123564707</v>
+        <v>123564758</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1957,10 +1925,10 @@
         <v>459953</v>
       </c>
       <c r="R12" t="n">
-        <v>7021635</v>
+        <v>7021620</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1989,7 +1957,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +1967,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,43 +1999,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123563664</v>
+        <v>123564909</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2076,13 +2048,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459959</v>
+        <v>459981</v>
       </c>
       <c r="R13" t="n">
-        <v>7021511</v>
+        <v>7021650</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2111,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2121,7 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog, 1 planta plus en vinterståndare</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,27 +2113,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123562820</v>
+        <v>123565029</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,7 +2155,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2202,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460020</v>
+        <v>459994</v>
       </c>
       <c r="R14" t="n">
-        <v>7021656</v>
+        <v>7021655</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2237,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2247,12 +2219,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 1 vinterståndare och 10 gröna plantor inom 50x50 cm, trolig fångstgrop intill</t>
+          <t>På marken i gammal granskog, 40 plantor och 2 vinterståndare inom 1x1m på liten kulle</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,15 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123564542</v>
+        <v>123565489</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2333,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459947</v>
+        <v>460067</v>
       </c>
       <c r="R15" t="n">
-        <v>7021620</v>
+        <v>7021711</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2368,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2378,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 11 plantor inom 3x1 m</t>
+          <t>På marken i gammal barrblandskog. 14 plantorninom 1,5x1,5 m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,42 +2377,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123564758</v>
+        <v>123564707</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2467,10 +2429,10 @@
         <v>459953</v>
       </c>
       <c r="R16" t="n">
-        <v>7021620</v>
+        <v>7021635</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2499,7 +2461,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2509,12 +2471,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På liten kulle, 3x1 m, ca 80 cm hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,52 +2503,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123564042</v>
+        <v>123563664</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2595,13 +2543,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459963</v>
+        <v>459959</v>
       </c>
       <c r="R17" t="n">
-        <v>7021536</v>
+        <v>7021511</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2630,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2640,12 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog, 43 exemplar inom 2x1 m yta. Ett par vinterståndare.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2660,74 +2603,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123561156</v>
+        <v>123561179</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sota, Ytterån, Näskott, Jmt</t>
+          <t>Sota, Sota, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460047</v>
+        <v>460052</v>
       </c>
       <c r="R18" t="n">
-        <v>7021716</v>
+        <v>7021702</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,12 +2695,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,15 +2715,127 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123561110</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sota, Sota, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>460053</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7021689</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10051-2025 artfynd.xlsx
+++ b/artfynd/A 10051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563516</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563035</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563701</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561156</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1492,6 +1527,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562820</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564042</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1870,6 +1920,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1996,6 +2051,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564758</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2122,6 +2182,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564909</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2248,6 +2313,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123565029</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2374,6 +2444,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123565489</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2500,6 +2575,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564707</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2612,6 +2692,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563664</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2724,6 +2809,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561179</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2836,8 +2926,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123561110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>